--- a/TEST_CASE_HOP_DEN.xlsx
+++ b/TEST_CASE_HOP_DEN.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truy vet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Can lam ro" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiem chung" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Huong dan'!$A$1:$B$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test cases'!$A$1:$Q$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Huong dan'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test cases'!$A$1:$S$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Truy vet'!$A$1:$C$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Can lam ro'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Can lam ro'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Kiem chung'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,233 +478,245 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Phiên bản</t>
+          <t>Nguồn SRS</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2.0 — sửa bộ cũ sau review. ID BB2-xxx mới; cột ID cũ giữ liên hệ BB-001…064. Số lượng tăng do tách đầu vào và thêm nhánh còn thiếu.</t>
+          <t>Đặc tả yêu cầu phần mềm website quản lý thư viện — SRS.docx; v1.0 ngày 16/10/2026; SHA-256 a440fa65c73192e27e82b27dee6a8bbef78505d31ae98023388250db3356e703. Chỉ lưu metadata/trích dẫn mục; không tự đưa file người dùng đính kèm lên GitHub.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Trạng thái</t>
+          <t>Phiên bản</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tất cả Chưa chạy. Chỉ rà soát thiết kế và kiểm tra cấu trúc file; không lấy kết quả API/browser trước đây làm kết quả bộ mới.</t>
+          <t>2.1 — đã đối chiếu SRS gốc do người dùng cung cấp và code tại acdb8a9. ID BB2-xxx mới; cột ID cũ giữ liên hệ BB-001…064. Số lượng tăng do tách đầu vào và thêm nhánh còn thiếu.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Môi trường test riêng, dữ liệu không phải production. Node/MySQL/app đã sẵn sàng; không có người ghi đồng thời trừ ca concurrency. MIN_PASSWORD_LENGTH=8, SESSION_HOURS=8, BLOCK_DUPLICATE_PENDING=true. Mỗi ca fixture mới, không phụ thuộc ca trước.</t>
+          <t>Các TC giữ Chưa chạy để không lẫn hồ sơ thực thi với mẫu thiết kế. Lượt review ngày 23/10/2026 đã chạy 19 tests có sẵn, browser workflow và 43 checks bổ trợ; có lỗi UI email xác nhận. Xem sheet Kiem chung và srs-code-review.md, không suy ra toàn bộ TC đã Pass.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Mọi path trong TC có prefix /api/v1; Content-Type application/json cho body. GUEST là jar rỗng. U1/U2 là hai USER khác nhau, A1 là ADMIN. A1 chuẩn bị dữ liệu, người thực hiện request mục tiêu theo tiền điều kiện.</t>
+          <t>Môi trường test riêng, dữ liệu không phải production. Node/MySQL/app đã sẵn sàng; không có người ghi đồng thời trừ ca concurrency. MIN_PASSWORD_LENGTH=8, SESSION_HOURS=8, BLOCK_DUPLICATE_PENDING=true. Mỗi ca fixture mới, không phụ thuộc ca trước.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RUN là 8 ký tự chữ/số duy nhất mỗi ca. {ID} lấy từ phản hồi tạo fixture. repeat(a,n) là CHUỖI gồm đúng n ký tự a, không phải biểu thức gửi nguyên văn. &lt;OMIT&gt; nghĩa là bỏ khóa JSON. Ca chuỗi 1 ký tự phải chọn ký tự còn trống hoặc fixture cô lập.</t>
+          <t>Mọi path trong TC có prefix /api/v1; Content-Type application/json cho body. GUEST là jar rỗng. U1/U2 là hai USER khác nhau, A1 là ADMIN. A1 chuẩn bị dữ liệu, người thực hiện request mục tiêu theo tiền điều kiện.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>RUN</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JSON nền: username=bb{RUN}, fullName=Nguyen An {RUN}, email=bb{RUN}@example.com, password=P. P là mật khẩu thử hợp lệ dài 12 ký tự do tester tạo và giữ cục bộ. Biến thể password có thể thay bằng chuỗi a đúng độ dài n; không áp quy tắc chữ hoa/ký tự đặc biệt.</t>
+          <t>RUN là 8 ký tự chữ/số duy nhất mỗi ca. {ID} lấy từ phản hồi tạo fixture. repeat(a,n) là CHUỖI gồm đúng n ký tự a, không phải biểu thức gửi nguyên văn. &lt;OMIT&gt; nghĩa là bỏ khóa JSON. Ca chuỗi 1 ký tự phải chọn ký tự còn trống hoặc fixture cô lập.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LOGIN</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>JSON username của tài khoản mục tiêu, password=P đã dùng khi tạo tài khoản đó; mỗi tài khoản jar riêng. P_NEW khác P, dài 12 ký tự. Không đưa mật khẩu/cookie/token vào bằng chứng hoặc Git.</t>
+          <t>JSON nền: username=bb{RUN}, fullName=Nguyen An {RUN}, email=bb{RUN}@example.com, password=P. P là mật khẩu thử hợp lệ dài 12 ký tự do tester tạo và giữ cục bộ. Biến thể password có thể thay bằng chuỗi a đúng độ dài n; không áp quy tắc chữ hoa/ký tự đặc biệt.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BOOK</t>
+          <t>LOGIN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>JSON nền: bookCode=CODE{RUN}, title=Sach {RUN}, author=Tacgia {RUN}, category=CAT{RUN}, totalQuantity=2; bỏ availableQuantity nếu TC không nói khác. Khi PUT giữ đủ bookCode,title,author,totalQuantity và giữ category/description hiện có để chỉ đổi biến mục tiêu.</t>
+          <t>JSON username của tài khoản mục tiêu, password=P đã dùng khi tạo tài khoản đó; mỗi tài khoản jar riêng. P_NEW khác P, dài 12 ký tự. Không đưa mật khẩu/cookie/token vào bằng chứng hoặc Git.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>USERPUT</t>
+          <t>BOOK</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>JSON giữ username, fullName, email hiện tại của tài khoản mục tiêu; bỏ password và role trừ khi TC yêu cầu thay. Tránh vô tình xóa email hoặc đổi trường không phải mục tiêu.</t>
+          <t>JSON nền: bookCode=CODE{RUN}, title=Sach {RUN}, author=Tacgia {RUN}, category=CAT{RUN}, totalQuantity=2; bỏ availableQuantity nếu TC không nói khác. Khi PUT giữ đủ bookCode,title,author,totalQuantity và giữ category/description hiện có để chỉ đổi biến mục tiêu.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BORROW</t>
+          <t>USERPUT</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>JSON nền: bookId=ID sách B1, borrowDate=D, dueDate=D+1. D là ngày thực hiện +1 ngày, dạng YYYY-MM-DD; cộng ngày theo lịch. Trường thiếu ID không được gửi dưới dạng chuỗi placeholder.</t>
+          <t>JSON giữ username, fullName, email hiện tại của tài khoản mục tiêu; bỏ password và role trừ khi TC yêu cầu thay. Tránh vô tình xóa email hoặc đổi trường không phải mục tiêu.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Fixtures trạng thái</t>
+          <t>BORROW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tạo B1 mới qua A1; đăng ký/đăng nhập U1/U2; tạo request bằng USER rồi APPROVE/DENY bằng A1. Để có PENDING với tồn 0: tạo 2 request khi tồn 1, duyệt request USER còn lại. Không sửa DB để dựng fixture hộp đen.</t>
+          <t>JSON nền: bookId=ID sách B1, borrowDate=D, dueDate=D+1. D là ngày thực hiện +1 ngày, dạng YYYY-MM-DD; cộng ngày theo lịch. Trường thiếu ID không được gửi dưới dạng chuỗi placeholder.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MISSING_ID</t>
+          <t>Fixtures trạng thái</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Chọn ID dương trong miền hợp đồng, xác nhận không có đối tượng mục tiêu qua GET danh sách đầy đủ hoặc GET chi tiết nếu được hỗ trợ; không suy luận từ một trang danh sách. Không có ghi đồng thời khi xác nhận.</t>
+          <t>Tạo B1 mới qua A1; đăng ký/đăng nhập U1/U2; tạo request bằng USER rồi APPROVE/DENY bằng A1. Để có PENDING với tồn 0: tạo 2 request khi tồn 1, duyệt request USER còn lại. Không sửa DB để dựng fixture hộp đen.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Chứng cứ</t>
+          <t>MISSING_ID</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mỗi TC ghi commit ứng dụng, cấu hình không bí mật, môi trường, browser, ngày giờ, input thực, HTTP/body đã che secret, mốc trước/sau. Lưu ID đối tượng và request ID; cookie không đưa vào báo cáo.</t>
+          <t>Chọn ID dương trong miền hợp đồng, xác nhận không có đối tượng mục tiêu qua GET danh sách đầy đủ hoặc GET chi tiết nếu được hỗ trợ; không suy luận từ một trang danh sách. Không có ghi đồng thời khi xác nhận.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Oracle chung</t>
+          <t>Chứng cứ</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>HTTP và nội dung/nghiệp vụ phải đồng thời đúng. Lỗi có success=false, error.code/message và requestId; không lộ SQL/stack/credential. Thành công JSON có success=true và data; 204 không body. Lỗi không làm thay đổi đối tượng nghiệp vụ.</t>
+          <t>Mỗi TC ghi commit ứng dụng, cấu hình không bí mật, môi trường, browser, ngày giờ, input thực, HTTP/body đã che secret, mốc trước/sau. Lưu ID đối tượng và request ID; cookie không đưa vào báo cáo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CLEANUP</t>
+          <t>Oracle chung</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng tạo thành công chưa có lịch sử: A1 DELETE sách/user thử sau ca. Có lịch sử: chỉ giữ trong môi trường test riêng; muốn reset phải dùng cơ chế môi trường test được cho phép, không xóa volume/DB có dữ liệu cần giữ. Không để cleanup làm mất bằng chứng.</t>
+          <t>HTTP và nội dung/nghiệp vụ phải đồng thời đúng. Lỗi có success=false, error.code/message và requestId; không lộ SQL/stack/credential. Thành công JSON có success=true và data; 204 không body. Lỗi không làm thay đổi đối tượng nghiệp vụ.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Thứ tự chạy</t>
+          <t>CLEANUP</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Chuẩn bị fixture độc lập, chạy P0 trước P1. Rate limit dùng instance/IP riêng hoặc chạy cuối. Hết hạn session cần 8 giờ, đánh dấu Chưa chạy/Blocked nếu chưa chờ đủ.</t>
+          <t>Đối tượng tạo thành công chưa có lịch sử: A1 DELETE sách/user thử sau ca. Có lịch sử: chỉ giữ trong môi trường test riêng; muốn reset phải dùng cơ chế môi trường test được cho phép, không xóa volume/DB có dữ liệu cần giữ. Không để cleanup làm mất bằng chứng.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Phân loại kết quả</t>
+          <t>Thứ tự chạy</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pass: mọi assertion đạt. Fail: sai khác có bằng chứng. Blocked: thiếu fixture/công cụ/đặc tả. Chưa chạy: chưa thực hiện. Các mục chưa chốt nằm riêng ở sheet Cần làm rõ, chưa tính là TC thực thi.</t>
+          <t>Chuẩn bị fixture độc lập, chạy P0 trước P1. Rate limit dùng instance/IP riêng hoặc chạy cuối. Hết hạn session cần 8 giờ, đánh dấu Chưa chạy/Blocked nếu chưa chờ đủ.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Phạm vi</t>
+          <t>Phân loại kết quả</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bao phủ FR-01…FR-12 theo tài liệu hiện có, không tuyên bố bao phủ toàn bộ SRS chưa có. Không gồm trả sách, gia hạn, phạt, thanh toán. Bộ này thiên về API hộp đen, có các ca UI riêng; không thay thế UAT toàn bộ màn hình.</t>
+          <t>Pass: mọi assertion đạt. Fail: sai khác có bằng chứng. Blocked: thiếu fixture/công cụ/đặc tả. Chưa chạy: chưa thực hiện. Các mục chưa chốt nằm riêng ở sheet Cần làm rõ, chưa tính là TC thực thi.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Phạm vi</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Đã đọc SRS v1.0 ngày 16/10/2026 do người dùng cung cấp (SHA-256 trong srs-code-review.md). Phủ các nhóm FR-01…12 nhưng vẫn còn mục TBD/NFR chưa được nghiệm thu. Không gồm trả sách, gia hạn, phạt, thanh toán. Bộ này thiên về API hộp đen, có các ca UI riêng; không thay thế UAT toàn bộ màn hình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Sinh lại file</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>python docs/blackbox/generate_workbook.py (cần openpyxl). Script chỉ sinh CSV/Markdown/Excel, không chạy ứng dụng hoặc sửa mã ứng dụng.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B20"/>
+  <autoFilter ref="A1:B21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -713,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q217"/>
+  <dimension ref="A1:S227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -733,6 +747,8 @@
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="90" customWidth="1" min="18" max="18"/>
+    <col width="85" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -821,6 +837,16 @@
           <t>Bằng chứng</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Căn cứ SRS / phạm vi</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Vị trí đối chiếu code (tĩnh)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -897,6 +923,16 @@
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -947,7 +983,7 @@
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1. POST /auth/register.
-2. A1 tìm username trong danh sách users.</t>
+2. A1 GET /admin/users?q={RUN}, duyệt mọi trang; không có ID mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -973,6 +1009,16 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1023,7 +1069,7 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1. POST /auth/register.
-2. A1 tìm username trong danh sách users.</t>
+2. A1 GET /admin/users?q={RUN}, duyệt mọi trang; không có ID mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1049,6 +1095,16 @@
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1099,7 +1155,7 @@
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1. POST /auth/register.
-2. A1 tìm username trong danh sách users.</t>
+2. A1 GET /admin/users?q={RUN}, duyệt mọi trang; không có ID mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1125,6 +1181,16 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1177,7 +1243,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1187,7 +1253,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1203,6 +1269,16 @@
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1255,7 +1331,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1281,6 +1357,16 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1333,7 +1419,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1359,6 +1445,16 @@
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1411,7 +1507,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1437,6 +1533,16 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1489,7 +1595,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1515,6 +1621,16 @@
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1567,7 +1683,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1577,7 +1693,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1593,6 +1709,16 @@
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1645,7 +1771,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1655,7 +1781,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1671,6 +1797,16 @@
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1723,7 +1859,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. POST /auth/login với tài khoản vừa tạo và mật khẩu đầu vào.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1749,6 +1885,16 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1801,7 +1947,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. POST /auth/login với tài khoản vừa tạo và mật khẩu đầu vào.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1827,6 +1973,16 @@
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1879,7 +2035,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. POST /auth/login với tài khoản vừa tạo và mật khẩu đầu vào.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1905,6 +2061,16 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
       <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1957,7 +2123,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. POST /auth/login với tài khoản vừa tạo và mật khẩu đầu vào.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1983,6 +2149,16 @@
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -2035,7 +2211,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -2045,7 +2221,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -2061,6 +2237,16 @@
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-07 / TBD-SEC-01 vẫn TBD; 8–128 theo decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2113,7 +2299,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2123,7 +2309,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2139,6 +2325,16 @@
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -2191,7 +2387,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -2217,6 +2413,16 @@
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2269,7 +2475,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2295,6 +2501,16 @@
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -2347,7 +2563,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -2373,6 +2589,16 @@
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr"/>
       <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2425,7 +2651,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2451,6 +2677,16 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -2503,7 +2739,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -2513,7 +2749,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2529,6 +2765,16 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2581,7 +2827,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2591,7 +2837,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2607,6 +2853,16 @@
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>SRS không chốt regex username; theo OpenAPI hiện tại.</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -2659,7 +2915,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -2669,7 +2925,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2685,6 +2941,16 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>SRS không chốt regex username; theo OpenAPI hiện tại.</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2737,7 +3003,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2763,6 +3029,16 @@
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>SRS không chốt regex username; theo OpenAPI hiện tại.</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -2839,6 +3115,16 @@
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr"/>
       <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2915,6 +3201,16 @@
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01: duy nhất nếu email bật; cấu hình bật theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -2967,7 +3263,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET /admin/users?q=username, xác nhận đúng ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -2993,6 +3289,16 @@
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01 / TBD-USER-01 vẫn TBD; email tùy chọn/định dạng theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3045,7 +3351,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET /admin/users?q=username, xác nhận đúng ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3071,6 +3377,16 @@
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01 / TBD-USER-01 vẫn TBD; email tùy chọn/định dạng theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -3123,7 +3439,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET /admin/users?q=username, xác nhận đúng ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -3149,6 +3465,16 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01 / TBD-USER-01 vẫn TBD; email tùy chọn/định dạng theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3201,7 +3527,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 GET /admin/users?q=username, xác nhận đúng ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -3227,6 +3553,16 @@
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01 / TBD-USER-01 vẫn TBD; email tùy chọn/định dạng theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -3279,7 +3615,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /auth/register.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /admin/users?q={RUN}, duyệt mọi trang (marker nằm trong username hoặc fullName không bị thay); đối chiếu ID trước/sau.</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -3289,7 +3625,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; không có ID tài khoản mới thuộc marker RUN.</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3305,6 +3641,16 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-01 / TBD-USER-01 vẫn TBD; email tùy chọn/định dạng theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3381,6 +3727,16 @@
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -3458,6 +3814,16 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; cookie session là lựa chọn bổ sung TBD-AUTH-01, không phải yêu cầu JWT bắt buộc.</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3535,6 +3901,16 @@
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02; cookie session là lựa chọn bổ sung TBD-AUTH-01, không phải yêu cầu JWT bắt buộc.</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -3611,6 +3987,16 @@
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3687,6 +4073,16 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -3765,6 +4161,16 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -3843,6 +4249,16 @@
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -3921,6 +4337,16 @@
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3999,6 +4425,16 @@
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -4075,6 +4511,16 @@
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>Rate-limit100/15 phút từ decisions.md; SRS không ấn định con số.</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -4150,6 +4596,16 @@
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>SRS TBD-BOOK-01: quyền Guest chưa chốt; TC401 theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -4225,6 +4681,16 @@
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr"/>
       <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>SRS TBD-BOOK-01: quyền Guest chưa chốt; TC401 theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -4301,6 +4767,16 @@
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -4377,6 +4853,16 @@
       <c r="O47" s="3" t="inlineStr"/>
       <c r="P47" s="3" t="inlineStr"/>
       <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -4453,6 +4939,16 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -4528,6 +5024,16 @@
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr"/>
       <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>SRS checklist: search case/accent chưa chốt; TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -4603,6 +5109,16 @@
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>SRS checklist: search case/accent chưa chốt; TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -4678,6 +5194,16 @@
       <c r="O51" s="3" t="inlineStr"/>
       <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4753,6 +5279,16 @@
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -4829,6 +5365,16 @@
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr"/>
       <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>SRS chỉ nêu sort; chiều A-Z/available theo nhãn UI và OpenAPI. newest tách Q-01.</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4905,6 +5451,16 @@
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>SRS chỉ nêu sort; chiều A-Z/available theo nhãn UI và OpenAPI. newest tách Q-01.</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -4980,6 +5536,16 @@
       <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="inlineStr"/>
       <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -5055,6 +5621,16 @@
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -5130,6 +5706,16 @@
       <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="3" t="inlineStr"/>
       <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -5205,6 +5791,16 @@
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -5280,6 +5876,16 @@
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr"/>
       <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -5355,6 +5961,16 @@
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr"/>
       <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -5430,6 +6046,16 @@
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -5505,6 +6131,16 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr"/>
       <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="150" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -5580,6 +6216,16 @@
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr"/>
       <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>SRS nêu pagination invalid; ngưỡng1/100 từ decisions.md/OpenAPI, không phải con số SRS.</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="150" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -5656,6 +6302,16 @@
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="150" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -5732,6 +6388,16 @@
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr"/>
       <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -5808,6 +6474,16 @@
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="150" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -5884,6 +6560,16 @@
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="150" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -5960,6 +6646,16 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="150" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -6036,6 +6732,16 @@
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
       <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="150" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -6111,6 +6817,16 @@
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Giới hạn query/enum từ OpenAPI; SRS nêu query phải hợp lệ.</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="150" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -6187,6 +6903,16 @@
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="inlineStr"/>
       <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="150" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -6263,6 +6989,16 @@
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr"/>
       <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="150" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -6339,6 +7075,16 @@
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="inlineStr"/>
       <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="150" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -6415,6 +7161,16 @@
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
       <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-03; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="150" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -6490,6 +7246,16 @@
       <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="3" t="inlineStr"/>
       <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>SRS checklist để pagination default TBD; default12 là decisions.md/OpenAPI.</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:70 (paging), :251 listBooks; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="150" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -6565,6 +7331,16 @@
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr"/>
       <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-04; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="150" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -6640,6 +7416,16 @@
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr"/>
       <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-04; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="150" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -6715,6 +7501,16 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr"/>
       <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-04; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="150" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -6790,6 +7586,16 @@
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="3" t="inlineStr"/>
       <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-04; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="150" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -6865,6 +7671,16 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
       <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-04; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:293; src/main.jsx:979 BookDetail</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="150" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -6941,6 +7757,16 @@
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="3" t="inlineStr"/>
       <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S81" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="150" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -7017,6 +7843,16 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr"/>
       <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="150" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -7093,6 +7929,16 @@
       <c r="O83" s="3" t="inlineStr"/>
       <c r="P83" s="3" t="inlineStr"/>
       <c r="Q83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="150" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -7169,6 +8015,16 @@
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr"/>
       <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="150" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -7221,7 +8077,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
@@ -7231,7 +8087,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -7247,6 +8103,16 @@
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="3" t="inlineStr"/>
       <c r="Q85" s="3" t="inlineStr"/>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S85" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="150" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -7299,7 +8165,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -7309,7 +8175,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7325,6 +8191,16 @@
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="150" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -7377,7 +8253,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
@@ -7387,7 +8263,7 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -7403,6 +8279,16 @@
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="3" t="inlineStr"/>
       <c r="Q87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S87" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="150" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -7455,7 +8341,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7465,7 +8351,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7481,6 +8367,16 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="150" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
@@ -7533,7 +8429,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -7543,7 +8439,7 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -7559,6 +8455,16 @@
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="3" t="inlineStr"/>
       <c r="Q89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S89" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="150" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -7611,7 +8517,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7621,7 +8527,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -7637,6 +8543,16 @@
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="150" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
@@ -7689,7 +8605,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -7699,7 +8615,7 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
@@ -7715,6 +8631,16 @@
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="3" t="inlineStr"/>
       <c r="Q91" s="3" t="inlineStr"/>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="150" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -7767,7 +8693,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /borrow-requests.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. U1 GET /me/borrow-requests và GET /books/{B1}; đối chiếu lịch sử/tồn trước khi gửi.</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7777,7 +8703,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>success=false; error.code=VALIDATION_ERROR; không tạo/sửa đối tượng.</t>
+          <t>success=false; error.code=VALIDATION_ERROR; lịch sử U1 không có yêu cầu mới; tồn B1 không đổi.</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -7793,6 +8719,16 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
       <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="150" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
@@ -7869,6 +8805,16 @@
       <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="3" t="inlineStr"/>
       <c r="Q93" s="3" t="inlineStr"/>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="150" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -7945,6 +8891,16 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr"/>
       <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="150" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
@@ -8021,6 +8977,16 @@
       <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="3" t="inlineStr"/>
       <c r="Q95" s="3" t="inlineStr"/>
+      <c r="R95" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="150" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -8097,6 +9063,16 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr"/>
       <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="150" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -8173,6 +9149,16 @@
       <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="inlineStr"/>
       <c r="Q97" s="3" t="inlineStr"/>
+      <c r="R97" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S97" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="150" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -8249,6 +9235,16 @@
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr"/>
       <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>SRS BR-18 / TBD-BORROW-03 còn TBD; chặn trùng là decisions.md.</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="150" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -8324,6 +9320,16 @@
       <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="3" t="inlineStr"/>
       <c r="Q99" s="3" t="inlineStr"/>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>SRS authorization matrix để TBD Admin mượn; TC403 theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S99" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="150" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -8400,6 +9406,16 @@
       <c r="O100" s="2" t="inlineStr"/>
       <c r="P100" s="2" t="inlineStr"/>
       <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05/FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm; server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="150" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
@@ -8476,6 +9492,16 @@
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="3" t="inlineStr"/>
       <c r="Q101" s="3" t="inlineStr"/>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-05/FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S101" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm; server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="150" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -8551,6 +9577,16 @@
       <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr"/>
       <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-06; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:129 (auth), :250 (/me); src/main.jsx:1709 Profile</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="150" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
@@ -8626,6 +9662,16 @@
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="3" t="inlineStr"/>
       <c r="Q103" s="3" t="inlineStr"/>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-06; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S103" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:129 (auth), :250 (/me); src/main.jsx:1709 Profile</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="150" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -8701,6 +9747,16 @@
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr"/>
       <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="150" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
@@ -8776,6 +9832,16 @@
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="3" t="inlineStr"/>
       <c r="Q105" s="3" t="inlineStr"/>
+      <c r="R105" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S105" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="150" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -8851,6 +9917,16 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr"/>
       <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="150" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
@@ -8926,6 +10002,16 @@
       <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="3" t="inlineStr"/>
       <c r="Q107" s="3" t="inlineStr"/>
+      <c r="R107" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S107" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="150" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -9001,6 +10087,16 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr"/>
       <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="150" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
@@ -9076,6 +10172,16 @@
       <c r="O109" s="3" t="inlineStr"/>
       <c r="P109" s="3" t="inlineStr"/>
       <c r="Q109" s="3" t="inlineStr"/>
+      <c r="R109" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S109" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="150" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -9152,6 +10258,16 @@
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr"/>
       <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-08 phụ thuộc cơ chế auth; thu hồi ngay theo session trong decisions.md.</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:235 logout; src/main.jsx:195 logout</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="150" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
@@ -9228,6 +10344,16 @@
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="3" t="inlineStr"/>
       <c r="Q111" s="3" t="inlineStr"/>
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="150" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -9304,6 +10430,16 @@
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr"/>
       <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="150" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
@@ -9380,6 +10516,16 @@
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="3" t="inlineStr"/>
       <c r="Q113" s="3" t="inlineStr"/>
+      <c r="R113" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S113" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="150" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -9456,6 +10602,16 @@
       <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr"/>
       <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="150" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
@@ -9532,6 +10688,16 @@
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="3" t="inlineStr"/>
       <c r="Q115" s="3" t="inlineStr"/>
+      <c r="R115" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="150" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -9608,6 +10774,16 @@
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="2" t="inlineStr"/>
       <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="150" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
@@ -9684,6 +10860,16 @@
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="3" t="inlineStr"/>
       <c r="Q117" s="3" t="inlineStr"/>
+      <c r="R117" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="150" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -9760,6 +10946,16 @@
       <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr"/>
       <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="150" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
@@ -9836,6 +11032,16 @@
       <c r="O119" s="3" t="inlineStr"/>
       <c r="P119" s="3" t="inlineStr"/>
       <c r="Q119" s="3" t="inlineStr"/>
+      <c r="R119" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S119" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="150" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -9912,6 +11118,16 @@
       <c r="O120" s="2" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr"/>
       <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="150" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
@@ -9988,6 +11204,16 @@
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr"/>
       <c r="Q121" s="3" t="inlineStr"/>
+      <c r="R121" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S121" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="150" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -10064,6 +11290,16 @@
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr"/>
       <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="150" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
@@ -10140,6 +11376,16 @@
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr"/>
       <c r="Q123" s="3" t="inlineStr"/>
+      <c r="R123" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S123" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="150" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -10216,6 +11462,16 @@
       <c r="O124" s="2" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr"/>
       <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="150" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
@@ -10292,6 +11548,16 @@
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr"/>
       <c r="Q125" s="3" t="inlineStr"/>
+      <c r="R125" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S125" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="150" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -10368,6 +11634,16 @@
       <c r="O126" s="2" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr"/>
       <c r="Q126" s="2" t="inlineStr"/>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="150" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
@@ -10444,6 +11720,16 @@
       <c r="O127" s="3" t="inlineStr"/>
       <c r="P127" s="3" t="inlineStr"/>
       <c r="Q127" s="3" t="inlineStr"/>
+      <c r="R127" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S127" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="150" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -10520,6 +11806,16 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr"/>
       <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="150" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
@@ -10596,6 +11892,16 @@
       <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="3" t="inlineStr"/>
       <c r="Q129" s="3" t="inlineStr"/>
+      <c r="R129" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S129" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="150" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -10672,6 +11978,16 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr"/>
       <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="150" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
@@ -10748,6 +12064,16 @@
       <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="3" t="inlineStr"/>
       <c r="Q131" s="3" t="inlineStr"/>
+      <c r="R131" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S131" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="150" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -10824,6 +12150,16 @@
       <c r="O132" s="2" t="inlineStr"/>
       <c r="P132" s="2" t="inlineStr"/>
       <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="150" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
@@ -10899,6 +12235,16 @@
       <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="3" t="inlineStr"/>
       <c r="Q133" s="3" t="inlineStr"/>
+      <c r="R133" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S133" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="150" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -10975,6 +12321,16 @@
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr"/>
       <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="150" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
@@ -11051,6 +12407,16 @@
       <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="3" t="inlineStr"/>
       <c r="Q135" s="3" t="inlineStr"/>
+      <c r="R135" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S135" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="150" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -11127,6 +12493,16 @@
       <c r="O136" s="2" t="inlineStr"/>
       <c r="P136" s="2" t="inlineStr"/>
       <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-09; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:400 stats; src/main.jsx:1374 Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="150" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
@@ -11203,6 +12579,16 @@
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr"/>
       <c r="Q137" s="3" t="inlineStr"/>
+      <c r="R137" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S137" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="150" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -11279,6 +12665,16 @@
       <c r="O138" s="2" t="inlineStr"/>
       <c r="P138" s="2" t="inlineStr"/>
       <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="150" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
@@ -11331,7 +12727,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -11357,6 +12753,16 @@
       <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="3" t="inlineStr"/>
       <c r="Q139" s="3" t="inlineStr"/>
+      <c r="R139" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S139" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="150" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -11409,7 +12815,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11435,6 +12841,16 @@
       <c r="O140" s="2" t="inlineStr"/>
       <c r="P140" s="2" t="inlineStr"/>
       <c r="Q140" s="2" t="inlineStr"/>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="150" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
@@ -11487,7 +12903,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
@@ -11513,6 +12929,16 @@
       <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="3" t="inlineStr"/>
       <c r="Q141" s="3" t="inlineStr"/>
+      <c r="R141" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S141" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="150" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -11565,7 +12991,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11591,6 +13017,16 @@
       <c r="O142" s="2" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr"/>
       <c r="Q142" s="2" t="inlineStr"/>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="150" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
@@ -11643,7 +13079,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -11669,6 +13105,16 @@
       <c r="O143" s="3" t="inlineStr"/>
       <c r="P143" s="3" t="inlineStr"/>
       <c r="Q143" s="3" t="inlineStr"/>
+      <c r="R143" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S143" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="150" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -11721,7 +13167,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11747,6 +13193,16 @@
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr"/>
       <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="150" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
@@ -11799,7 +13255,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -11825,6 +13281,16 @@
       <c r="O145" s="3" t="inlineStr"/>
       <c r="P145" s="3" t="inlineStr"/>
       <c r="Q145" s="3" t="inlineStr"/>
+      <c r="R145" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S145" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="150" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -11877,7 +13343,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11903,6 +13369,16 @@
       <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr"/>
       <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="150" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
@@ -11955,7 +13431,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -11981,6 +13457,16 @@
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="3" t="inlineStr"/>
       <c r="Q147" s="3" t="inlineStr"/>
+      <c r="R147" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S147" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="150" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -12033,7 +13519,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -12059,6 +13545,16 @@
       <c r="O148" s="2" t="inlineStr"/>
       <c r="P148" s="2" t="inlineStr"/>
       <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="150" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
@@ -12111,7 +13607,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -12137,6 +13633,16 @@
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="3" t="inlineStr"/>
       <c r="Q149" s="3" t="inlineStr"/>
+      <c r="R149" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S149" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="150" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -12189,7 +13695,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -12215,6 +13721,16 @@
       <c r="O150" s="2" t="inlineStr"/>
       <c r="P150" s="2" t="inlineStr"/>
       <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="150" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
@@ -12267,7 +13783,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -12293,6 +13809,16 @@
       <c r="O151" s="3" t="inlineStr"/>
       <c r="P151" s="3" t="inlineStr"/>
       <c r="Q151" s="3" t="inlineStr"/>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S151" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="150" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -12345,7 +13871,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -12371,6 +13897,16 @@
       <c r="O152" s="2" t="inlineStr"/>
       <c r="P152" s="2" t="inlineStr"/>
       <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="150" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
@@ -12423,7 +13959,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -12449,6 +13985,16 @@
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
       <c r="Q153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S153" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="150" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -12501,7 +14047,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -12527,6 +14073,16 @@
       <c r="O154" s="2" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr"/>
       <c r="Q154" s="2" t="inlineStr"/>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="150" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
@@ -12579,7 +14135,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 GET danh sách users hoặc GET /books/{ID mới} tùy đối tượng để xác nhận dữ liệu.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -12605,6 +14161,16 @@
       <c r="O155" s="3" t="inlineStr"/>
       <c r="P155" s="3" t="inlineStr"/>
       <c r="Q155" s="3" t="inlineStr"/>
+      <c r="R155" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S155" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="150" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -12657,7 +14223,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12683,6 +14249,16 @@
       <c r="O156" s="2" t="inlineStr"/>
       <c r="P156" s="2" t="inlineStr"/>
       <c r="Q156" s="2" t="inlineStr"/>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="150" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
@@ -12735,7 +14311,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -12761,6 +14337,16 @@
       <c r="O157" s="3" t="inlineStr"/>
       <c r="P157" s="3" t="inlineStr"/>
       <c r="Q157" s="3" t="inlineStr"/>
+      <c r="R157" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S157" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="150" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -12813,7 +14399,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. GET /books/{ID mới} bằng A1, xác nhận totalQuantity và availableQuantity.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12839,6 +14425,16 @@
       <c r="O158" s="2" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr"/>
       <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="150" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
@@ -12891,7 +14487,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. GET /books/{ID mới} bằng A1, xác nhận totalQuantity và availableQuantity.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
@@ -12917,6 +14513,16 @@
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="3" t="inlineStr"/>
       <c r="Q159" s="3" t="inlineStr"/>
+      <c r="R159" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S159" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="150" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -12969,7 +14575,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. GET /books/{ID mới} bằng A1, xác nhận totalQuantity và availableQuantity.</t>
+4. GET /books/{ID mới} bằng A1; đối chiếu các trường và tổng/tồn.</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12995,6 +14601,16 @@
       <c r="O160" s="2" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr"/>
       <c r="Q160" s="2" t="inlineStr"/>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="150" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
@@ -13047,7 +14663,7 @@
           <t>1. Chuẩn bị dữ liệu nền mới.
 2. Gửi POST /admin/books.
 3. Đọc phản hồi.
-4. A1 tìm đúng username hoặc bookCode mới qua danh sách công khai phù hợp, xác nhận không có ID mới.</t>
+4. A1 GET /books?category=CAT{RUN}, duyệt mọi trang; danh sách vẫn rỗng, không có ID sách mới.</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
@@ -13073,6 +14689,16 @@
       <c r="O161" s="3" t="inlineStr"/>
       <c r="P161" s="3" t="inlineStr"/>
       <c r="Q161" s="3" t="inlineStr"/>
+      <c r="R161" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S161" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="150" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -13149,6 +14775,16 @@
       <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr"/>
       <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>SRS BR-10 quy định bất đẳng thức; quyền nhập available khi tạo vẫn TBD, TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="150" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
@@ -13225,6 +14861,16 @@
       <c r="O163" s="3" t="inlineStr"/>
       <c r="P163" s="3" t="inlineStr"/>
       <c r="Q163" s="3" t="inlineStr"/>
+      <c r="R163" s="3" t="inlineStr">
+        <is>
+          <t>SRS BR-10 quy định bất đẳng thức; quyền nhập available khi tạo vẫn TBD, TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S163" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="150" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -13301,6 +14947,16 @@
       <c r="O164" s="2" t="inlineStr"/>
       <c r="P164" s="2" t="inlineStr"/>
       <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>SRS BR-10 quy định bất đẳng thức; quyền nhập available khi tạo vẫn TBD, TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="150" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
@@ -13377,6 +15033,16 @@
       <c r="O165" s="3" t="inlineStr"/>
       <c r="P165" s="3" t="inlineStr"/>
       <c r="Q165" s="3" t="inlineStr"/>
+      <c r="R165" s="3" t="inlineStr">
+        <is>
+          <t>SRS BR-10 quy định bất đẳng thức; quyền nhập available khi tạo vẫn TBD, TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S165" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="150" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -13453,6 +15119,16 @@
       <c r="O166" s="2" t="inlineStr"/>
       <c r="P166" s="2" t="inlineStr"/>
       <c r="Q166" s="2" t="inlineStr"/>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>SRS BR-10 quy định bất đẳng thức; quyền nhập available khi tạo vẫn TBD, TC theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="150" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
@@ -13529,6 +15205,16 @@
       <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="3" t="inlineStr"/>
       <c r="Q167" s="3" t="inlineStr"/>
+      <c r="R167" s="3" t="inlineStr">
+        <is>
+          <t>SRS BR-10; quy tắc sửa tổng giữ số đang mượn là decisions.md.</t>
+        </is>
+      </c>
+      <c r="S167" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="150" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -13605,6 +15291,16 @@
       <c r="O168" s="2" t="inlineStr"/>
       <c r="P168" s="2" t="inlineStr"/>
       <c r="Q168" s="2" t="inlineStr"/>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>SRS BR-10; quy tắc sửa tổng giữ số đang mượn là decisions.md.</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="150" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
@@ -13681,6 +15377,16 @@
       <c r="O169" s="3" t="inlineStr"/>
       <c r="P169" s="3" t="inlineStr"/>
       <c r="Q169" s="3" t="inlineStr"/>
+      <c r="R169" s="3" t="inlineStr">
+        <is>
+          <t>SRS BR-10; quy tắc sửa tổng giữ số đang mượn là decisions.md.</t>
+        </is>
+      </c>
+      <c r="S169" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="150" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -13757,6 +15463,16 @@
       <c r="O170" s="2" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr"/>
       <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="150" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
@@ -13833,6 +15549,16 @@
       <c r="O171" s="3" t="inlineStr"/>
       <c r="P171" s="3" t="inlineStr"/>
       <c r="Q171" s="3" t="inlineStr"/>
+      <c r="R171" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S171" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="150" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -13909,6 +15635,16 @@
       <c r="O172" s="2" t="inlineStr"/>
       <c r="P172" s="2" t="inlineStr"/>
       <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="150" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
@@ -13986,6 +15722,16 @@
       <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="3" t="inlineStr"/>
       <c r="Q173" s="3" t="inlineStr"/>
+      <c r="R173" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S173" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="150" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -14063,6 +15809,16 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr"/>
       <c r="Q174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
@@ -14140,6 +15896,16 @@
       <c r="O175" s="3" t="inlineStr"/>
       <c r="P175" s="3" t="inlineStr"/>
       <c r="Q175" s="3" t="inlineStr"/>
+      <c r="R175" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S175" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="150" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -14217,6 +15983,16 @@
       <c r="O176" s="2" t="inlineStr"/>
       <c r="P176" s="2" t="inlineStr"/>
       <c r="Q176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="150" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
@@ -14293,6 +16069,16 @@
       <c r="O177" s="3" t="inlineStr"/>
       <c r="P177" s="3" t="inlineStr"/>
       <c r="Q177" s="3" t="inlineStr"/>
+      <c r="R177" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S177" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="150" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -14369,6 +16155,16 @@
       <c r="O178" s="2" t="inlineStr"/>
       <c r="P178" s="2" t="inlineStr"/>
       <c r="Q178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="150" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
@@ -14445,6 +16241,16 @@
       <c r="O179" s="3" t="inlineStr"/>
       <c r="P179" s="3" t="inlineStr"/>
       <c r="Q179" s="3" t="inlineStr"/>
+      <c r="R179" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S179" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="150" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -14521,6 +16327,16 @@
       <c r="O180" s="2" t="inlineStr"/>
       <c r="P180" s="2" t="inlineStr"/>
       <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="150" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
@@ -14598,6 +16414,16 @@
       <c r="O181" s="3" t="inlineStr"/>
       <c r="P181" s="3" t="inlineStr"/>
       <c r="Q181" s="3" t="inlineStr"/>
+      <c r="R181" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S181" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="150" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -14675,6 +16501,16 @@
       <c r="O182" s="2" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr"/>
       <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="150" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
@@ -14751,6 +16587,16 @@
       <c r="O183" s="3" t="inlineStr"/>
       <c r="P183" s="3" t="inlineStr"/>
       <c r="Q183" s="3" t="inlineStr"/>
+      <c r="R183" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S183" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="150" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -14827,6 +16673,16 @@
       <c r="O184" s="2" t="inlineStr"/>
       <c r="P184" s="2" t="inlineStr"/>
       <c r="Q184" s="2" t="inlineStr"/>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="150" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
@@ -14903,6 +16759,16 @@
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="3" t="inlineStr"/>
       <c r="Q185" s="3" t="inlineStr"/>
+      <c r="R185" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="150" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -14979,6 +16845,16 @@
       <c r="O186" s="2" t="inlineStr"/>
       <c r="P186" s="2" t="inlineStr"/>
       <c r="Q186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="150" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
@@ -15054,6 +16930,16 @@
       <c r="O187" s="3" t="inlineStr"/>
       <c r="P187" s="3" t="inlineStr"/>
       <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S187" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="150" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -15129,6 +17015,16 @@
       <c r="O188" s="2" t="inlineStr"/>
       <c r="P188" s="2" t="inlineStr"/>
       <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="150" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
@@ -15204,6 +17100,16 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr"/>
       <c r="Q189" s="3" t="inlineStr"/>
+      <c r="R189" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S189" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="150" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -15279,6 +17185,16 @@
       <c r="O190" s="2" t="inlineStr"/>
       <c r="P190" s="2" t="inlineStr"/>
       <c r="Q190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="150" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
@@ -15354,6 +17270,16 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr"/>
       <c r="Q191" s="3" t="inlineStr"/>
+      <c r="R191" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-11; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S191" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348, :490, :491 (decisions); src/main.jsx:1191 Requests, :1318 DecisionForm</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="150" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -15430,6 +17356,16 @@
       <c r="O192" s="2" t="inlineStr"/>
       <c r="P192" s="2" t="inlineStr"/>
       <c r="Q192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="150" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
@@ -15506,6 +17442,16 @@
       <c r="O193" s="3" t="inlineStr"/>
       <c r="P193" s="3" t="inlineStr"/>
       <c r="Q193" s="3" t="inlineStr"/>
+      <c r="R193" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S193" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="150" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -15583,6 +17529,16 @@
       <c r="O194" s="2" t="inlineStr"/>
       <c r="P194" s="2" t="inlineStr"/>
       <c r="Q194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="150" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
@@ -15659,6 +17615,16 @@
       <c r="O195" s="3" t="inlineStr"/>
       <c r="P195" s="3" t="inlineStr"/>
       <c r="Q195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S195" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="150" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -15735,6 +17701,16 @@
       <c r="O196" s="2" t="inlineStr"/>
       <c r="P196" s="2" t="inlineStr"/>
       <c r="Q196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="150" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
@@ -15811,6 +17787,16 @@
       <c r="O197" s="3" t="inlineStr"/>
       <c r="P197" s="3" t="inlineStr"/>
       <c r="Q197" s="3" t="inlineStr"/>
+      <c r="R197" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S197" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="150" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -15887,6 +17873,16 @@
       <c r="O198" s="2" t="inlineStr"/>
       <c r="P198" s="2" t="inlineStr"/>
       <c r="Q198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="150" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
@@ -15965,6 +17961,16 @@
       <c r="O199" s="3" t="inlineStr"/>
       <c r="P199" s="3" t="inlineStr"/>
       <c r="Q199" s="3" t="inlineStr"/>
+      <c r="R199" s="3" t="inlineStr">
+        <is>
+          <t>SRS không quy định cụ thể thu hồi session sau đổi password; theo OpenAPI/decisions.md.</t>
+        </is>
+      </c>
+      <c r="S199" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="150" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -16042,6 +18048,16 @@
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="inlineStr"/>
       <c r="Q200" s="2" t="inlineStr"/>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; thu hồi session sau đổi role theo OpenAPI; quản trị ADMIN khác còn TBD.</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="150" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
@@ -16118,6 +18134,16 @@
       <c r="O201" s="3" t="inlineStr"/>
       <c r="P201" s="3" t="inlineStr"/>
       <c r="Q201" s="3" t="inlineStr"/>
+      <c r="R201" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12 / TBD-ADMIN-01 còn TBD; tự bảo vệ ADMIN theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S201" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="150" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -16194,6 +18220,16 @@
       <c r="O202" s="2" t="inlineStr"/>
       <c r="P202" s="2" t="inlineStr"/>
       <c r="Q202" s="2" t="inlineStr"/>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12 / TBD-ADMIN-01 còn TBD; tự bảo vệ ADMIN theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="150" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
@@ -16270,6 +18306,16 @@
       <c r="O203" s="3" t="inlineStr"/>
       <c r="P203" s="3" t="inlineStr"/>
       <c r="Q203" s="3" t="inlineStr"/>
+      <c r="R203" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S203" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="150" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -16347,6 +18393,16 @@
       <c r="O204" s="2" t="inlineStr"/>
       <c r="P204" s="2" t="inlineStr"/>
       <c r="Q204" s="2" t="inlineStr"/>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="150" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
@@ -16422,6 +18478,16 @@
       <c r="O205" s="3" t="inlineStr"/>
       <c r="P205" s="3" t="inlineStr"/>
       <c r="Q205" s="3" t="inlineStr"/>
+      <c r="R205" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S205" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="150" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -16497,6 +18563,16 @@
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr"/>
       <c r="Q206" s="2" t="inlineStr"/>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-10; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:56 bookSchema, :413 create, :441 update, :481 delete; src/main.jsx:1102 BookForm</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="150" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
@@ -16572,6 +18648,16 @@
       <c r="O207" s="3" t="inlineStr"/>
       <c r="P207" s="3" t="inlineStr"/>
       <c r="Q207" s="3" t="inlineStr"/>
+      <c r="R207" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S207" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="150" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
@@ -16647,6 +18733,16 @@
       <c r="O208" s="2" t="inlineStr"/>
       <c r="P208" s="2" t="inlineStr"/>
       <c r="Q208" s="2" t="inlineStr"/>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="150" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
@@ -16724,6 +18820,16 @@
       <c r="O209" s="3" t="inlineStr"/>
       <c r="P209" s="3" t="inlineStr"/>
       <c r="Q209" s="3" t="inlineStr"/>
+      <c r="R209" s="3" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-08 / TBD-AUTH-02 còn TBD; 8 giờ theo decisions.md.</t>
+        </is>
+      </c>
+      <c r="S209" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:129 auth, :217 session expiry</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="150" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -16800,6 +18906,16 @@
       <c r="O210" s="2" t="inlineStr"/>
       <c r="P210" s="2" t="inlineStr"/>
       <c r="Q210" s="2" t="inlineStr"/>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC; Origin check là cơ chế session/same-origin bổ sung trong decisions.md.</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:13 helmet, :150 Origin, :251 listBooks, :638 error handler; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="150" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
@@ -16875,6 +18991,16 @@
       <c r="O211" s="3" t="inlineStr"/>
       <c r="P211" s="3" t="inlineStr"/>
       <c r="Q211" s="3" t="inlineStr"/>
+      <c r="R211" s="3" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-04/05 về input/error; ca SQL/HTML bổ trợ kiểm tra bảo mật web, không thay penetration test.</t>
+        </is>
+      </c>
+      <c r="S211" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:13 helmet, :150 Origin, :251 listBooks, :638 error handler; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="150" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -16952,6 +19078,16 @@
       <c r="O212" s="2" t="inlineStr"/>
       <c r="P212" s="2" t="inlineStr"/>
       <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>SRS NFR-SEC-04/05 về input/error; ca SQL/HTML bổ trợ kiểm tra bảo mật web, không thay penetration test.</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:13 helmet, :150 Origin, :251 listBooks, :638 error handler; src/main.jsx:676 Catalog</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="150" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
@@ -17030,6 +19166,16 @@
       <c r="O213" s="3" t="inlineStr"/>
       <c r="P213" s="3" t="inlineStr"/>
       <c r="Q213" s="3" t="inlineStr"/>
+      <c r="R213" s="3" t="inlineStr">
+        <is>
+          <t>Ca UI bổ sung; SRS chưa chốt viewport 1440/390 hoặc tiêu chí responsive chi tiết.</t>
+        </is>
+      </c>
+      <c r="S213" s="3" t="inlineStr">
+        <is>
+          <t>src/main.jsx:167 App, :648 Pagination, :676 Catalog; src/style.css</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="150" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -17108,6 +19254,16 @@
       <c r="O214" s="2" t="inlineStr"/>
       <c r="P214" s="2" t="inlineStr"/>
       <c r="Q214" s="2" t="inlineStr"/>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>Ca UI bổ sung; SRS chưa chốt viewport 1440/390 hoặc tiêu chí responsive chi tiết.</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>src/main.jsx:167 App, :648 Pagination, :676 Catalog; src/style.css</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="150" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
@@ -17186,6 +19342,16 @@
       <c r="O215" s="3" t="inlineStr"/>
       <c r="P215" s="3" t="inlineStr"/>
       <c r="Q215" s="3" t="inlineStr"/>
+      <c r="R215" s="3" t="inlineStr">
+        <is>
+          <t>Ca UI bổ sung; SRS chưa chốt viewport 1440/390 hoặc tiêu chí responsive chi tiết.</t>
+        </is>
+      </c>
+      <c r="S215" s="3" t="inlineStr">
+        <is>
+          <t>src/main.jsx:167 App, :648 Pagination, :676 Catalog; src/style.css</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="150" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -17264,6 +19430,16 @@
       <c r="O216" s="2" t="inlineStr"/>
       <c r="P216" s="2" t="inlineStr"/>
       <c r="Q216" s="2" t="inlineStr"/>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>Ca UI bổ sung; SRS chưa chốt viewport 1440/390 hoặc tiêu chí responsive chi tiết.</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>src/main.jsx:167 App, :648 Pagination, :676 Catalog; src/style.css</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="150" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
@@ -17341,11 +19517,878 @@
       <c r="O217" s="3" t="inlineStr"/>
       <c r="P217" s="3" t="inlineStr"/>
       <c r="Q217" s="3" t="inlineStr"/>
+      <c r="R217" s="3" t="inlineStr">
+        <is>
+          <t>Ca UI bổ sung; SRS chưa chốt viewport 1440/390 hoặc tiêu chí responsive chi tiết.</t>
+        </is>
+      </c>
+      <c r="S217" s="3" t="inlineStr">
+        <is>
+          <t>src/main.jsx:167 App, :648 Pagination, :676 Catalog; src/style.css</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="150" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>BB2-217</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>FR-06</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Guest bị chặn /me</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-06/07; BR-03; HTTP conventions</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>BASE; GUEST</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>GET /me</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>1. GET không kèm cookie.</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>UNAUTHENTICATED; không trả hồ sơ/lịch sử.</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr"/>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr"/>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-06; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:129 (auth), :250 (/me); src/main.jsx:1709 Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="150" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>BB2-218</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>FR-07</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Guest bị chặn /me/borrow-requests</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-06/07; BR-03; HTTP conventions</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>BASE; GUEST</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>GET /me/borrow-requests</t>
+        </is>
+      </c>
+      <c r="J219" s="3" t="inlineStr">
+        <is>
+          <t>1. GET không kèm cookie.</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>UNAUTHENTICATED; không trả hồ sơ/lịch sử.</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="inlineStr"/>
+      <c r="P219" s="3" t="inlineStr"/>
+      <c r="Q219" s="3" t="inlineStr"/>
+      <c r="R219" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S219" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="150" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>BB2-219</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Guest không tạo được yêu cầu</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; BR-11</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>BASE; GUEST; B1 tồn tại</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>BORROW</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /borrow-requests không cookie.
+2. A1 kiểm tra danh sách requests.</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>UNAUTHENTICATED; không tạo yêu cầu, tồn không đổi.</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-05; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:300 (dates), :308 (create); src/main.jsx:1018 BorrowForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="150" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>BB2-220</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>FR-06</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Session không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-06; NFR-SEC-04</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>BASE; Cookie library_session=invalidtoken; không phải cookie thật</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>GET /me</t>
+        </is>
+      </c>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t>1. GET /me kèm cookie giả.</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>UNAUTHENTICATED; không lộ hồ sơ.</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O221" s="3" t="inlineStr"/>
+      <c r="P221" s="3" t="inlineStr"/>
+      <c r="Q221" s="3" t="inlineStr"/>
+      <c r="R221" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-06; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S221" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:129 (auth), :250 (/me); src/main.jsx:1709 Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="150" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>BB2-221</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Đăng nhập API bằng email</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02: username/email + password</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>BASE; U1 có email=bb{RUN}@example.com đã cấu hình</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>LOGIN username=email U1, password=P</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /auth/login bằng jar mới.
+2. GET /me.</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>200; GET: 200</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>data.user.id=U1; /me đúng U1; có phiên hợp lệ.</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr"/>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr"/>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="150" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>BB2-222</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Đăng nhập UI bằng email dài hơn 64</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; dictionary email VARCHAR(254); OpenAPI Login.username max254</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>BASE; A1 tạo U1 có email=repeat(a,60)+@ui{RUN}.example.com; tổng 83 ký tự; browser Chromium; bắt đầu GUEST</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>Email 83 ký tự hợp lệ; password=P của U1</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t>1. Xác nhận API LOGIN với email này trả 200 rồi logout.
+2. Mở form đăng nhập bằng browser.
+3. Nhập đầy đủ email bằng thao tác bàn phím; nhập password.
+4. Bấm Đăng nhập; quan sát giá trị ô, HTTP và màn hình.</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>API: 200; UI LOGIN: 200; /me: 200</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>Ô đăng nhập giữ đủ 83 ký tự; đăng nhập thành công, vào Khám phá sách; /me đúng U1. Không sửa kỳ vọng thành 401 theo lỗi hiện tại.</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O223" s="3" t="inlineStr"/>
+      <c r="P223" s="3" t="inlineStr"/>
+      <c r="Q223" s="3" t="inlineStr"/>
+      <c r="R223" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-02; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S223" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:168 (rate limit), :200 (login); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="150" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>BB2-223</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>POST role không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12 ngoại lệ role invalid; role USER/ADMIN</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>BASE; A1; U2 là USER còn tồn tại</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>REG mới role=INVALID</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /admin/users.
+2. Đọc lại danh sách/đối tượng.</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>VALIDATION_ERROR; không tạo mới; không đổi role/thuộc tính U2.</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr"/>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr"/>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="150" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>BB2-224</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>PUT role không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12 ngoại lệ role invalid; role USER/ADMIN</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>BASE; A1; U2 là USER còn tồn tại</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>USERPUT U2 role=INVALID</t>
+        </is>
+      </c>
+      <c r="J225" s="3" t="inlineStr">
+        <is>
+          <t>1. PUT /admin/users/{U2}.
+2. Đọc lại danh sách/đối tượng.</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>VALIDATION_ERROR; không tạo mới; không đổi role/thuộc tính U2.</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O225" s="3" t="inlineStr"/>
+      <c r="P225" s="3" t="inlineStr"/>
+      <c r="Q225" s="3" t="inlineStr"/>
+      <c r="R225" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-12; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S225" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:539 list, :554 create, :568 update, :605 delete; src/main.jsx:1497 UserList, :1606 UserForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="150" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>BB2-225</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>JSON không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>SRS HTTP conventions; NFR-MNT-02; NFR-SEC-04/05</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>BASE; GUEST</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>Content-Type application/json; raw body={"username":</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /auth/register với raw body đúng như trên, không dùng JSON serializer tự sửa.</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>error.code=INVALID_JSON; success=false; không lộ stack/SQL.</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr"/>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>SRS FR-01; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>server/app.js:37 (schemas), :186 (register); src/main.jsx:507 AuthForm</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="150" customHeight="1">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>BB2-226</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>SRS-review</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>FR-07</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Phân trang lịch sử sai</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Phân vùng tương đương</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07 ngoại lệ pagination invalid; OpenAPI page minimum1</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>BASE; U1</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>GET /me/borrow-requests?page=0</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>1. Gửi GET bằng U1.</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>VALIDATION_ERROR; không trả danh sách thành công.</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>Đọc lại đối tượng bằng API nếu có thay đổi. Giữ bằng chứng; dọn theo CLEANUP trong Hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="O227" s="3" t="inlineStr"/>
+      <c r="P227" s="3" t="inlineStr"/>
+      <c r="Q227" s="3" t="inlineStr"/>
+      <c r="R227" s="3" t="inlineStr">
+        <is>
+          <t>SRS FR-07; chi tiết mã lỗi/trường JSON theo OpenAPI. Đối chiếu tĩnh, không đồng nghĩa TC đã chạy.</t>
+        </is>
+      </c>
+      <c r="S227" s="3" t="inlineStr">
+        <is>
+          <t>server/app.js:348 listRequests, :396 (own); src/main.jsx:1191 Requests</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q217"/>
+  <autoFilter ref="A1:S227"/>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N217" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Trạng thái không hợp lệ" error="Chọn một trạng thái trong danh sách." type="list" errorStyle="stop">
+    <dataValidation sqref="N2:N227" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Trạng thái không hợp lệ" error="Chọn một trạng thái trong danh sách." type="list" errorStyle="stop">
       <formula1>"Chưa chạy,Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17391,11 +20434,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BB2-001, BB2-002, BB2-003, BB2-004, BB2-005, BB2-006, BB2-007, BB2-008, BB2-009, BB2-010, BB2-011, BB2-012, BB2-013, BB2-014, BB2-015, BB2-016, BB2-017, BB2-018, BB2-019, BB2-020, BB2-021, BB2-022, BB2-023, BB2-024, BB2-025, BB2-026, BB2-027, BB2-028, BB2-029, BB2-030, BB2-031, BB2-032, BB2-033</t>
+          <t>BB2-001, BB2-002, BB2-003, BB2-004, BB2-005, BB2-006, BB2-007, BB2-008, BB2-009, BB2-010, BB2-011, BB2-012, BB2-013, BB2-014, BB2-015, BB2-016, BB2-017, BB2-018, BB2-019, BB2-020, BB2-021, BB2-022, BB2-023, BB2-024, BB2-025, BB2-026, BB2-027, BB2-028, BB2-029, BB2-030, BB2-031, BB2-032, BB2-033, BB2-225</t>
         </is>
       </c>
     </row>
@@ -17406,11 +20449,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BB2-034, BB2-035, BB2-036, BB2-037, BB2-038, BB2-039, BB2-040, BB2-041, BB2-042</t>
+          <t>BB2-034, BB2-035, BB2-036, BB2-037, BB2-038, BB2-039, BB2-040, BB2-041, BB2-042, BB2-221, BB2-222</t>
         </is>
       </c>
     </row>
@@ -17451,11 +20494,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BB2-080, BB2-081, BB2-082, BB2-083, BB2-084, BB2-085, BB2-086, BB2-087, BB2-088, BB2-089, BB2-090, BB2-091, BB2-092, BB2-093, BB2-094, BB2-095, BB2-096, BB2-097, BB2-098, BB2-099, BB2-100</t>
+          <t>BB2-080, BB2-081, BB2-082, BB2-083, BB2-084, BB2-085, BB2-086, BB2-087, BB2-088, BB2-089, BB2-090, BB2-091, BB2-092, BB2-093, BB2-094, BB2-095, BB2-096, BB2-097, BB2-098, BB2-099, BB2-100, BB2-219</t>
         </is>
       </c>
     </row>
@@ -17466,11 +20509,11 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BB2-101, BB2-102</t>
+          <t>BB2-101, BB2-102, BB2-217, BB2-220</t>
         </is>
       </c>
     </row>
@@ -17481,11 +20524,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BB2-103, BB2-104, BB2-105, BB2-106, BB2-107, BB2-108</t>
+          <t>BB2-103, BB2-104, BB2-105, BB2-106, BB2-107, BB2-108, BB2-218, BB2-226</t>
         </is>
       </c>
     </row>
@@ -17556,11 +20599,11 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>BB2-124, BB2-125, BB2-126, BB2-127, BB2-128, BB2-129, BB2-130, BB2-131, BB2-191, BB2-192, BB2-193, BB2-194, BB2-195, BB2-196, BB2-197, BB2-198, BB2-199, BB2-200, BB2-201, BB2-202, BB2-203, BB2-206, BB2-207</t>
+          <t>BB2-124, BB2-125, BB2-126, BB2-127, BB2-128, BB2-129, BB2-130, BB2-131, BB2-191, BB2-192, BB2-193, BB2-194, BB2-195, BB2-196, BB2-197, BB2-198, BB2-199, BB2-200, BB2-201, BB2-202, BB2-203, BB2-206, BB2-207, BB2-223, BB2-224</t>
         </is>
       </c>
     </row>
@@ -17621,7 +20664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17726,44 +20769,215 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>SRS gốc và giới hạn triển khai</t>
+          <t>Giới hạn triển khai ngoài SRS</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Không có SRS gốc trong checkout. Static review thấy giới hạn totalQuantity 1.000.000, ID và độ dài category/description trong mã chưa đầy đủ trong OpenAPI.</t>
+          <t>Đã nhận SRS v1.0 ngày 16/10/2026. SRS dùng BIGINT UNSIGNED trong dictionary; code dùng INT và path max2147483647; totalQuantity max1.000.000 và description max10.000 chưa được chốt trong SRS.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Không tự thêm các giới hạn này làm chuẩn nghiệm thu. Đối chiếu/phê duyệt SRS và hợp đồng API rồi bổ sung biên trên.</t>
+          <t>Đây là khác biệt thiết kế/contract cần xác nhận, không tự gắn thành requirement đã được duyệt.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="110" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Q-06</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TBD của SRS so với decisions.md</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SRS vẫn để TBD: auth/session/expiry, password, email, quyền Guest, Admin mượn, duplicate pending, quyền sửa tồn và tự quản lý ADMIN. decisions.md ghi các lựa chọn triển khai; SRS tải lên chưa cập nhật chúng.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>TC của các chính sách này chỉ là kiểm tra contract/cấu hình hiện tại, chưa đủ để kết luận đạt SRS nếu thiếu phê duyệt thay đổi yêu cầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Q-07</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mâu thuẫn quyền lịch sử Admin trong SRS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>API catalog ghi /me/borrow-requests: User; authorization matrix ghi Admin được own borrow history. Code chỉ yêu cầu auth nên Admin cũng gọi được.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Cần chốt và cập nhật SRS; chưa kết luận code vi phạm ở mục này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Q-05</t>
         </is>
       </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NFR và audit/rollback</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có ngưỡng SLA/p95/RPO/RTO hoặc API đọc audit và cơ chế gây lỗi hạ tầng được hỗ trợ.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Không đánh dấu các yêu cầu này đạt. Bộ hiện tại không thay thế load test, penetration test, kiểm thử khôi phục hoặc kiểm thử hộp trắng rollback.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="145" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kết quả / giới hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Đã đọc bản gốc v1.0; có nhiều TBD và mâu thuẫn quyền Admin/history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PASS npm run build; warning chunk-size không chặn build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tests có sẵn</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>19/19 PASS; không phải toàn bộ bộ TC mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Browser có sẵn</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PASS reader borrow, admin approve, CRUD book, users/profile/mobile; no pageerror.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Checks bổ trợ</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NFR và audit/rollback</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Chưa có ngưỡng SLA/p95/RPO/RTO hoặc API đọc audit và cơ chế gây lỗi hạ tầng được hỗ trợ.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Không đánh dấu các yêu cầu này đạt. Bộ hiện tại không thay thế load test, penetration test, kiểm thử khôi phục hoặc kiểm thử hộp trắng rollback.</t>
+          <t>43/43 assertions đạt; 33 registration, 8 invalid-date, 2 quan sát API. Hai quan sát không phải kết luận web đạt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="85" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi web xác nhận</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>BUG-01: email83 ký tự đăng nhập API200; formmaxlength64 cắt còn64, UI401. TC BB2-222 kỳ vọng thành công, chưa sửa ứng dụng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="85" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sai lệch nhãn</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>BUG-02: newest có nhãn Mới cập nhật nhưng sắp id DESC; chờ chốt định nghĩa theo Q-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="85" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Giới hạn</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Chưa chạy toàn bộ TC, rate-limit100/15 và phiên8giờ chưa chạy trong review. Không tự ghi Pass vào bộ mẫu. Bằng chứng trong evidence/ và srs-code-review.md.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TEST_CASE_HOP_DEN.xlsx
+++ b/TEST_CASE_HOP_DEN.xlsx
@@ -525,7 +525,7 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. Bấm Đăng ký độc giả.
-2. Nhập dữ liệu trên, bấm Đăng ký.
+2. Nhập dữ liệu trên, bấm Tạo tài khoản.
 3. Đăng nhập tài khoản vừa tạo.</t>
         </is>
       </c>
@@ -571,7 +571,7 @@
         <is>
           <t>1. Mở Đăng ký độc giả.
 2. Điền họ tên/mật khẩu, để trống tên đăng nhập.
-3. Bấm Đăng ký.</t>
+3. Bấm Tạo tài khoản.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -612,7 +612,7 @@
         <is>
           <t>1. Mở Đăng ký độc giả.
 2. Dùng username readerRUN, họ tên/mật khẩu hợp lệ.
-3. Bấm Đăng ký.</t>
+3. Bấm Tạo tài khoản.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
